--- a/veriler.xlsx
+++ b/veriler.xlsx
@@ -24,13 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Oksijen</t>
-  </si>
-  <si>
-    <t>Detay</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Karbon</t>
   </si>
@@ -41,13 +35,13 @@
     <t>Y</t>
   </si>
   <si>
-    <t>Ad</t>
-  </si>
-  <si>
     <t>Ihlamur</t>
   </si>
   <si>
-    <t>FJHVJHV</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Tür</t>
   </si>
 </sst>
 </file>
@@ -370,51 +364,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1">
+      <c r="C2">
+        <v>7.5</v>
+      </c>
+      <c r="D2" s="1">
         <v>416161.97659999999</v>
       </c>
-      <c r="C2" s="1">
+      <c r="E2" s="1">
         <v>4559748.2867000001</v>
-      </c>
-      <c r="D2">
-        <v>7.5</v>
-      </c>
-      <c r="E2">
-        <v>6.2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
